--- a/data/trans_orig/IP16_n_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33301</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41265</t>
+          <t>42367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29814</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44819</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>60633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81555</t>
+          <t>81743</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53705</t>
+          <t>53245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>42977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86821</t>
+          <t>86633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107140</t>
+          <t>107743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14854</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31694</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>42572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>57125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67125</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91926</t>
+          <t>91403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118712</t>
+          <t>118594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76068</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94551</t>
+          <t>94759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>149904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176572</t>
+          <t>177095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37520</t>
+          <t>37559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23668</t>
+          <t>24046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40560</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64568</t>
+          <t>64190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77232</t>
+          <t>76832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79844</t>
+          <t>80295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91672</t>
+          <t>91936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148710</t>
+          <t>147743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166219</t>
+          <t>165578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27298</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34381</t>
+          <t>34287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37095</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59588</t>
+          <t>59578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>69877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>60077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18924</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32524</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66478</t>
+          <t>65858</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75706</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66696</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77344</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136075</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151035</t>
+          <t>151445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +4675,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>6855</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>3448</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>11723</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>20,33%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>6855</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3498</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>11623</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28237</t>
+          <t>28182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,47 +4788,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>50806</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>45938</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>54213</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>79,67%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>50806</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>46038</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>54163</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>79,84%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>45101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>47365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75733</t>
+          <t>75742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>104531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69523</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86947</t>
+          <t>86403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151185</t>
+          <t>151243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190711</t>
+          <t>193502</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>39034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65615</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49952</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73332</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>130359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16_n_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3484</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7342</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3878</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10981</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11483</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10472</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14001</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10156</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16774</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14706</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11067</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18170</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10565</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18074</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>66,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14001</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9786</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16963</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>33219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36904</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30140</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44537</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>34240</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27462</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>42367</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>27332</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>41106</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>42,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>36904</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>30008</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44692</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>42,09%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60633</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81743</t>
+          <t>81322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50765</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43132</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>57529</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>57,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>46467</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>38340</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53245</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>39601</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53375</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>57,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50765</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>42977</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>57661</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>57,91%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86633</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107743</t>
+          <t>106782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9300</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19031</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6354</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3263</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9949</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9755</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14103</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9800</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19174</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,99%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21163</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16235</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25966</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16197</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12602</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19288</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12796</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19220</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21163</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>16092</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25466</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>60,01%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42572</t>
+          <t>42926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57263</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48114</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>47937</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39714</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57125</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>39115</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57055</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>38,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>48434</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>66155</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>39,99%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91403</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118594</t>
+          <t>118223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85930</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>76072</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>95079</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77368</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>68180</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85591</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>68250</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86190</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>85930</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>77038</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>94759</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>60,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149904</t>
+          <t>150275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177095</t>
+          <t>175780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2012 (tasa de respuesta: 99,54%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5053</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2509</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8519</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1814</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16293</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12935</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17529</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18008</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14542</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20552</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14517</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20562</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16293</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13572</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17531</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37559</t>
+          <t>37441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14427</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9620</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21834</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16584</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11404</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24046</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24381</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14427</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9098</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>22819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79200</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91414</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>64190</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76832</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>63855</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>77444</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86607</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>80295</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91936</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147743</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165578</t>
+          <t>166451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5603</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10629</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>4833</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9270</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9146</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5603</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2415</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9854</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33830</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28804</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36770</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31571</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27134</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34287</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27258</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34091</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33830</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29579</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37018</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59578</t>
+          <t>59452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>70276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30041</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>26470</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18904</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35340</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19392</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34820</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21844</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15323</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30154</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37709</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>60635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136730</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>128533</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>143317</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>121231</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>112361</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128797</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>112881</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>128309</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>136730</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>128420</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143251</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246197</t>
+          <t>245639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268565</t>
+          <t>268062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147701</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4383</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7385</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15127</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13242</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,41%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>83,49%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7385</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>50,11%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12958</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7798</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19041</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11209</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6948</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17121</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6863</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16599</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12958</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8343</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18575</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32378</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72662</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66579</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77822</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>71770</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65858</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76031</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>66380</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>76116</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>72662</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>67045</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>77277</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136221</t>
+          <t>136424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151445</t>
+          <t>150927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5784</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4216</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8306</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8444</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6220</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>26232</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23086</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28218</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>24576</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20486</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26886</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20348</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27062</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>26232</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22650</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>28182</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>54060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,74 +4958,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23909</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15989</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10393</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22664</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10223</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22667</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>17,78%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11485</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24391</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106278</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>99367</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>111756</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>111472</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>104797</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>117068</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>104794</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>82,22%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>106278</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>98885</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>111791</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208473</t>
+          <t>207826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225537</t>
+          <t>225888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8548</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2265</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5583</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5372</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11616</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12965</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9647</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,13%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27363</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37341</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29524</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46636</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>32199</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16312</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45101</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>26,65%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51374</t>
+          <t>38828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>68527</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47365</t>
+          <t>57545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>80683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70571</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61276</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78388</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>56,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>88644</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>75742</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>104531</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>78234</t>
+          <t>61499</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68650</t>
+          <t>53856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86403</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>166878</t>
+          <t>132069</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151243</t>
+          <t>119913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193502</t>
+          <t>143051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18882</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16199</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11767</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21719</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30158</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29875</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32552</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65082</t>
+          <t>61584</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46133</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>66628</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30581</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>64467</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>40244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>58311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85984</t>
+          <t>93209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130359</t>
+          <t>120878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>108997</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>98324</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>118819</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>127052</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>113248</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>147134</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>120997</t>
+          <t>93364</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109441</t>
+          <t>84681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132174</t>
+          <t>102748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>202361</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>229557</t>
+          <t>187066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273932</t>
+          <t>214735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
